--- a/marketing_forms/050_influencer_authenticity_validation_form--marketing_forms.xlsx
+++ b/marketing_forms/050_influencer_authenticity_validation_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'13-18',_'label':_'13-18'}</t>
+          <t>13-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': '13-18', 'label': '13-18'}</t>
+          <t>13-18</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'19-24',_'label':_'19-24'}</t>
+          <t>19-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '19-24', 'label': '19-24'}</t>
+          <t>19-24</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'25-34',_'label':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': '25-34', 'label': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'35-44',_'label':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': '35-44', 'label': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'45-54',_'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': '45-54', 'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'usa',_'label':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'USA', 'label': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'canada',_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Canada', 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'mexico',_'label':_'mexico'}</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Mexico', 'label': 'Mexico'}</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'asian',_'label':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Asian', 'label': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'black',_'label':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Black', 'label': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'hispanic',_'label':_'hispanic'}</t>
+          <t>hispanic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Hispanic', 'label': 'Hispanic'}</t>
+          <t>Hispanic</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'white',_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'White', 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'video',_'label':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'video', 'label': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'photo',_'label':_'photo'}</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'photo', 'label': 'Photo'}</t>
+          <t>Photo</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'post',_'label':_'post'}</t>
+          <t>post</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'post', 'label': 'Post'}</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'live_stream',_'label':_'live_stream'}</t>
+          <t>live_stream</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'live_stream', 'label': 'Live Stream'}</t>
+          <t>Live Stream</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'strong',_'label':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'strong', 'label': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'weak',_'label':_'weak'}</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'weak', 'label': 'Weak'}</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'none', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
